--- a/CollectaMundo/TestFiles/AllCombinations.xlsx
+++ b/CollectaMundo/TestFiles/AllCombinations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\CollectaMundo\TestFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\CollectaMundo\CollectaMundo\TestFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E0717C9-3428-4490-B382-6E7D645502C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAB3830-BF9A-405E-BCD3-17834744B556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Combinations" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Adventure</t>
+  </si>
+  <si>
+    <t>Disse to collapses til sidst</t>
   </si>
 </sst>
 </file>
@@ -446,15 +449,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -475,7 +484,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -498,7 +507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -521,7 +530,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -547,7 +556,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -570,7 +579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -596,7 +605,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -619,8 +628,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
@@ -640,7 +651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -666,14 +677,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -693,22 +704,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
       <c r="B12" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>11</v>
@@ -716,14 +729,19 @@
       <c r="H12" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3"/>
+      <c r="I12" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
       <c r="B13" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>5</v>
@@ -732,7 +750,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>11</v>
@@ -740,22 +758,25 @@
       <c r="H13" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="I13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -778,7 +799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>

--- a/CollectaMundo/TestFiles/AllCombinations.xlsx
+++ b/CollectaMundo/TestFiles/AllCombinations.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\CollectaMundo\CollectaMundo\TestFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\CollectaMundo\TestFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAB3830-BF9A-405E-BCD3-17834744B556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0D19A5-9DD2-4704-B660-4B6E66E31CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Combinations" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="38">
   <si>
     <t>Name</t>
   </si>
@@ -77,6 +90,63 @@
   </si>
   <si>
     <t>Disse to collapses til sidst</t>
+  </si>
+  <si>
+    <t>Sokrates, Athenian Teacher</t>
+  </si>
+  <si>
+    <t>rare</t>
+  </si>
+  <si>
+    <t>ACR</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Defender, Sokratic Dialogue</t>
+  </si>
+  <si>
+    <t>Assassin's Creed</t>
+  </si>
+  <si>
+    <t>Viashino Runner</t>
+  </si>
+  <si>
+    <t>common</t>
+  </si>
+  <si>
+    <t>USG</t>
+  </si>
+  <si>
+    <t>Menace</t>
+  </si>
+  <si>
+    <t>Urza's Saga</t>
+  </si>
+  <si>
+    <t>Prismatic Ending</t>
+  </si>
+  <si>
+    <t>uncommon</t>
+  </si>
+  <si>
+    <t>MH2</t>
+  </si>
+  <si>
+    <t>Converge</t>
+  </si>
+  <si>
+    <t>Modern Horizons 2</t>
+  </si>
+  <si>
+    <t>Staying Power</t>
+  </si>
+  <si>
+    <t>UND</t>
+  </si>
+  <si>
+    <t>Unsanctioned</t>
   </si>
 </sst>
 </file>
@@ -449,21 +519,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -484,7 +555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -506,8 +577,26 @@
       <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -529,8 +618,26 @@
       <c r="G3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -556,7 +663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -578,8 +685,29 @@
       <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -605,7 +733,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -627,8 +755,29 @@
       <c r="G7" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -650,8 +799,26 @@
       <c r="G8" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -677,14 +844,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -704,7 +871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -733,7 +900,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -762,21 +929,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -799,7 +966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
